--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schaej17\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D99962-4042-4E22-9E87-3876B41AF8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAEF7C0-17EE-419F-93CC-8CEDA5C55698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4692" yWindow="2208" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020 Roster" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="114">
   <si>
     <t>Kaspar</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>marcel.wolbers@bayer.com</t>
+  </si>
+  <si>
+    <t>Website Manager</t>
   </si>
 </sst>
 </file>
@@ -907,6 +910,9 @@
       <c r="E7" s="2">
         <v>1</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">

--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schaej17\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAEF7C0-17EE-419F-93CC-8CEDA5C55698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47315B9-6251-4487-AE32-0AD7D682B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,9 +269,6 @@
     <t>UCB</t>
   </si>
   <si>
-    <t>NextGen representative</t>
-  </si>
-  <si>
     <t>Baldur</t>
   </si>
   <si>
@@ -362,9 +359,6 @@
     <t>Previtali</t>
   </si>
   <si>
-    <t>Suisse Romande representative</t>
-  </si>
-  <si>
     <t>aiesha.zia@novartis.com</t>
   </si>
   <si>
@@ -381,6 +375,12 @@
   </si>
   <si>
     <t>Website Manager</t>
+  </si>
+  <si>
+    <t>NextGen Representative</t>
+  </si>
+  <si>
+    <t>Suisse Romande Representative</t>
   </si>
 </sst>
 </file>
@@ -845,10 +845,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -979,10 +979,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -1061,16 +1061,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1"/>
       <c r="G16" s="2" t="s">
@@ -1150,16 +1150,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -1168,41 +1168,41 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -1210,16 +1210,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -1227,16 +1227,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -1244,16 +1244,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -1261,22 +1261,22 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1298,16 +1298,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
